--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="117">
   <si>
     <t>#</t>
   </si>
@@ -393,6 +393,33 @@
   </si>
   <si>
     <t>极雀战靴</t>
+  </si>
+  <si>
+    <t>极玄精粹</t>
+  </si>
+  <si>
+    <t>极玄神剑</t>
+  </si>
+  <si>
+    <t>极玄神甲</t>
+  </si>
+  <si>
+    <t>极玄面罩</t>
+  </si>
+  <si>
+    <t>极玄项链</t>
+  </si>
+  <si>
+    <t>极玄护腕</t>
+  </si>
+  <si>
+    <t>极玄护戒</t>
+  </si>
+  <si>
+    <t>极玄腰带</t>
+  </si>
+  <si>
+    <t>极玄战靴</t>
   </si>
 </sst>
 </file>
@@ -1376,7 +1403,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O110"/>
+  <dimension ref="C1:O119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -4817,8 +4844,306 @@
       <c r="O109" s="4"/>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="5"/>
       <c r="N110" s="2"/>
       <c r="O110" s="4"/>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C111" s="1">
+        <v>1071</v>
+      </c>
+      <c r="D111" s="1">
+        <v>9</v>
+      </c>
+      <c r="E111" s="4">
+        <v>4058</v>
+      </c>
+      <c r="F111" s="4">
+        <v>150</v>
+      </c>
+      <c r="G111" s="4">
+        <v>50</v>
+      </c>
+      <c r="H111" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I111" s="4">
+        <v>10</v>
+      </c>
+      <c r="J111" s="4">
+        <v>0</v>
+      </c>
+      <c r="K111" s="4">
+        <v>0</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="4"/>
+    </row>
+    <row r="112" customHeight="1" spans="3:15">
+      <c r="C112" s="1">
+        <v>1072</v>
+      </c>
+      <c r="D112" s="1">
+        <v>9</v>
+      </c>
+      <c r="E112" s="4">
+        <v>61000065</v>
+      </c>
+      <c r="F112" s="4">
+        <v>1</v>
+      </c>
+      <c r="G112" s="4">
+        <v>50</v>
+      </c>
+      <c r="H112" s="4">
+        <v>400</v>
+      </c>
+      <c r="I112" s="4">
+        <v>10</v>
+      </c>
+      <c r="J112" s="4">
+        <v>0</v>
+      </c>
+      <c r="K112" s="4">
+        <v>0</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:12">
+      <c r="C113" s="1">
+        <v>1073</v>
+      </c>
+      <c r="D113" s="1">
+        <v>9</v>
+      </c>
+      <c r="E113" s="4">
+        <v>61000066</v>
+      </c>
+      <c r="F113" s="4">
+        <v>1</v>
+      </c>
+      <c r="G113" s="4">
+        <v>50</v>
+      </c>
+      <c r="H113" s="4">
+        <v>400</v>
+      </c>
+      <c r="I113" s="4">
+        <v>10</v>
+      </c>
+      <c r="J113" s="4">
+        <v>0</v>
+      </c>
+      <c r="K113" s="4">
+        <v>0</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:12">
+      <c r="C114" s="1">
+        <v>1074</v>
+      </c>
+      <c r="D114" s="1">
+        <v>9</v>
+      </c>
+      <c r="E114" s="4">
+        <v>61000067</v>
+      </c>
+      <c r="F114" s="4">
+        <v>1</v>
+      </c>
+      <c r="G114" s="4">
+        <v>150</v>
+      </c>
+      <c r="H114" s="4">
+        <v>450</v>
+      </c>
+      <c r="I114" s="4">
+        <v>10</v>
+      </c>
+      <c r="J114" s="4">
+        <v>0</v>
+      </c>
+      <c r="K114" s="4">
+        <v>0</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:12">
+      <c r="C115" s="1">
+        <v>1075</v>
+      </c>
+      <c r="D115" s="1">
+        <v>9</v>
+      </c>
+      <c r="E115" s="4">
+        <v>61000068</v>
+      </c>
+      <c r="F115" s="4">
+        <v>1</v>
+      </c>
+      <c r="G115" s="4">
+        <v>150</v>
+      </c>
+      <c r="H115" s="4">
+        <v>450</v>
+      </c>
+      <c r="I115" s="4">
+        <v>10</v>
+      </c>
+      <c r="J115" s="4">
+        <v>0</v>
+      </c>
+      <c r="K115" s="4">
+        <v>0</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:12">
+      <c r="C116" s="1">
+        <v>1076</v>
+      </c>
+      <c r="D116" s="1">
+        <v>9</v>
+      </c>
+      <c r="E116" s="4">
+        <v>61000069</v>
+      </c>
+      <c r="F116" s="4">
+        <v>1</v>
+      </c>
+      <c r="G116" s="4">
+        <v>300</v>
+      </c>
+      <c r="H116" s="4">
+        <v>650</v>
+      </c>
+      <c r="I116" s="4">
+        <v>10</v>
+      </c>
+      <c r="J116" s="4">
+        <v>0</v>
+      </c>
+      <c r="K116" s="4">
+        <v>0</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:12">
+      <c r="C117" s="1">
+        <v>1077</v>
+      </c>
+      <c r="D117" s="1">
+        <v>9</v>
+      </c>
+      <c r="E117" s="4">
+        <v>61000070</v>
+      </c>
+      <c r="F117" s="4">
+        <v>1</v>
+      </c>
+      <c r="G117" s="4">
+        <v>300</v>
+      </c>
+      <c r="H117" s="4">
+        <v>650</v>
+      </c>
+      <c r="I117" s="4">
+        <v>10</v>
+      </c>
+      <c r="J117" s="4">
+        <v>0</v>
+      </c>
+      <c r="K117" s="4">
+        <v>0</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:12">
+      <c r="C118" s="1">
+        <v>1078</v>
+      </c>
+      <c r="D118" s="1">
+        <v>9</v>
+      </c>
+      <c r="E118" s="4">
+        <v>61000071</v>
+      </c>
+      <c r="F118" s="4">
+        <v>1</v>
+      </c>
+      <c r="G118" s="4">
+        <v>400</v>
+      </c>
+      <c r="H118" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I118" s="4">
+        <v>10</v>
+      </c>
+      <c r="J118" s="4">
+        <v>0</v>
+      </c>
+      <c r="K118" s="4">
+        <v>0</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:12">
+      <c r="C119" s="1">
+        <v>1079</v>
+      </c>
+      <c r="D119" s="1">
+        <v>9</v>
+      </c>
+      <c r="E119" s="4">
+        <v>61000072</v>
+      </c>
+      <c r="F119" s="4">
+        <v>1</v>
+      </c>
+      <c r="G119" s="4">
+        <v>400</v>
+      </c>
+      <c r="H119" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I119" s="4">
+        <v>10</v>
+      </c>
+      <c r="J119" s="4">
+        <v>0</v>
+      </c>
+      <c r="K119" s="4">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5" t="s">
+        <v>116</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
